--- a/Data/Hires/TestDataBelgiumMKv02.xlsx
+++ b/Data/Hires/TestDataBelgiumMKv02.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9ECE256-2549-45AC-9AC5-EB34344DF6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8D5D05-B564-4E02-ACD3-09512514D096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,6 @@
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="128">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -229,12 +228,6 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10698808</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>751 Retail Team 1 (Rykec Puvyjo (10528834) (Inherited))</t>
   </si>
   <si>
@@ -377,9 +370,6 @@
   </si>
   <si>
     <t>Test2</t>
-  </si>
-  <si>
-    <t>10698797</t>
   </si>
   <si>
     <t>751 Store Management (Rykec Puvyjo (10528834))</t>
@@ -1261,45 +1251,41 @@
       <c r="A2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="E2" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="F2" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="G2" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="H2" s="17" t="s">
         <v>70</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>72</v>
       </c>
       <c r="I2" s="18">
         <v>25041111</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L2" s="19">
         <f t="shared" ref="L2" ca="1" si="0">TODAY()-31</f>
-        <v>45752</v>
+        <v>45773</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N2" s="20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O2" s="18">
         <v>38</v>
@@ -1308,44 +1294,44 @@
         <v>1000</v>
       </c>
       <c r="Q2" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="S2" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="T2" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="U2" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="T2" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="U2" s="22" t="s">
-        <v>79</v>
-      </c>
       <c r="V2" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="W2" s="23">
         <f t="shared" ref="W2" ca="1" si="1">L2</f>
-        <v>45752</v>
+        <v>45773</v>
       </c>
       <c r="X2" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y2" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z2" t="s">
         <v>80</v>
       </c>
-      <c r="Y2" s="24" t="s">
+      <c r="AA2" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>82</v>
       </c>
-      <c r="AA2" s="25" t="s">
+      <c r="AC2" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>52</v>
@@ -1354,162 +1340,157 @@
         <v>35</v>
       </c>
       <c r="AF2" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AH2" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="AH2" s="19" t="s">
+      <c r="AJ2" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="AI2" s="18" t="s">
+      <c r="AK2" t="s">
         <v>89</v>
       </c>
-      <c r="AJ2" s="18" t="s">
+      <c r="AL2" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM2" s="28" t="s">
         <v>90</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL2" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM2" s="28" t="s">
-        <v>92</v>
       </c>
       <c r="AN2" s="1">
         <f t="array" aca="1" ref="AN2:AN3" ca="1">_xlfn.RANDARRAY(2,1,12345678901,99999999999,TRUE)</f>
-        <v>39528592432</v>
+        <v>90131241829</v>
       </c>
       <c r="AO2" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP2" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ2" s="20" t="s">
         <v>93</v>
-      </c>
-      <c r="AP2" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ2" s="20" t="s">
-        <v>95</v>
       </c>
       <c r="AR2" s="19" t="str">
         <f>AH2</f>
         <v>N/A</v>
       </c>
       <c r="AS2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AT2" s="29">
         <v>35591</v>
       </c>
       <c r="AU2" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AV2" s="28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AW2" s="30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AX2" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="AY2" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ2" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="AY2" s="31" t="s">
+      <c r="BA2" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB2" t="s">
         <v>98</v>
       </c>
-      <c r="AZ2" s="30" t="s">
+      <c r="BC2" t="s">
         <v>99</v>
       </c>
-      <c r="BA2" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB2" t="s">
+      <c r="BD2" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BE2" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="BD2" s="14" t="s">
+      <c r="BF2" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="BE2" s="28" t="s">
+      <c r="BG2" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="BF2" s="32" t="s">
+      <c r="BH2" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="BG2" s="28" t="s">
+      <c r="BI2" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="BH2" s="28" t="s">
+      <c r="BJ2" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="BI2" s="28" t="s">
+      <c r="BK2" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="BJ2" s="30" t="s">
+      <c r="BL2" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BK2" s="30" t="s">
+      <c r="BM2" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="BL2" s="30" t="s">
+      <c r="BN2" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="BM2" s="30" t="s">
+      <c r="BO2" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="BN2" s="30" t="s">
+      <c r="BP2" s="33" t="s">
         <v>112</v>
-      </c>
-      <c r="BO2" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="BP2" s="33" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:68" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="G3" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="H3" s="17" t="s">
         <v>117</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>120</v>
       </c>
       <c r="I3" s="18">
         <v>25041111</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L3" s="19">
         <f t="shared" ref="L3" ca="1" si="2">TODAY()-31</f>
-        <v>45752</v>
+        <v>45773</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N3" s="20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O3" s="18">
         <v>38</v>
@@ -1518,44 +1499,44 @@
         <v>1000</v>
       </c>
       <c r="Q3" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="R3" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="S3" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="T3" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="R3" s="18" t="s">
+      <c r="U3" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="S3" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="T3" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="U3" s="22" t="s">
-        <v>79</v>
-      </c>
       <c r="V3" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="W3" s="23">
         <f t="shared" ref="W3" ca="1" si="3">L3</f>
-        <v>45752</v>
+        <v>45773</v>
       </c>
       <c r="X3" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Y3" s="24" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Z3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AA3" s="25" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AB3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AD3" s="1" t="s">
         <v>52</v>
@@ -1564,118 +1545,118 @@
         <v>35</v>
       </c>
       <c r="AF3" s="14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AH3" s="19">
         <f ca="1">TODAY()+365</f>
-        <v>46148</v>
+        <v>46169</v>
       </c>
       <c r="AI3" s="18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AJ3" s="18" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AK3" s="1">
         <v>251</v>
       </c>
       <c r="AL3" s="28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AM3" s="28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AN3" s="1">
         <f ca="1"/>
-        <v>84868708785</v>
+        <v>38394683643</v>
       </c>
       <c r="AO3" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP3" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ3" s="20" t="s">
         <v>93</v>
-      </c>
-      <c r="AP3" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="AQ3" s="20" t="s">
-        <v>95</v>
       </c>
       <c r="AR3" s="19">
         <f t="shared" ref="AR3" ca="1" si="4">AH3</f>
-        <v>46148</v>
+        <v>46169</v>
       </c>
       <c r="AS3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AT3" s="29">
         <v>35591</v>
       </c>
       <c r="AU3" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AV3" s="28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AW3" s="30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AX3" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="AY3" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ3" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="AY3" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="AZ3" s="30" t="s">
-        <v>99</v>
-      </c>
       <c r="BA3" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="BB3" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD3" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="BE3" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="BF3" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="BG3" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="BH3" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="BI3" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="BJ3" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="BK3" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="BC3" t="s">
-        <v>128</v>
-      </c>
-      <c r="BD3" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="BE3" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="BF3" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="BG3" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="BH3" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="BI3" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="BJ3" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="BK3" s="30" t="s">
-        <v>130</v>
-      </c>
       <c r="BL3" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM3" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="BN3" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="BM3" s="30" t="s">
+      <c r="BO3" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="BN3" s="30" t="s">
+      <c r="BP3" s="33" t="s">
         <v>112</v>
-      </c>
-      <c r="BO3" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="BP3" s="33" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>
